--- a/outputs/daily/hr_rankings_2026-08-20_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20_full.xlsx
@@ -5014,34 +5014,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5298,34 +5294,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6142,34 +6134,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10322,34 +10310,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -15886,34 +15870,30 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -19782,34 +19762,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -29250,34 +29226,30 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -37050,34 +37022,30 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -40398,34 +40366,30 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -50484,34 +50448,30 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -50768,34 +50728,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -51612,34 +51568,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>

--- a/outputs/daily/hr_rankings_2026-08-20_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-20_full.xlsx
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>66.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1929,7 +1929,7 @@
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>71.59999999999999</v>
+        <v>51.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1981,22 +1981,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>28.1</v>
+        <v>30.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/32, 0 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9671,47 +9671,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>642715</t>
+          <t>682987</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Willy Adames</t>
+          <t>Spencer Jones</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T22:35:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9734,61 +9734,65 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>36.7</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Q34" t="n">
-        <v>56.1</v>
+        <v>32.9</v>
       </c>
       <c r="R34" t="n">
-        <v>39.6</v>
+        <v>32.1</v>
       </c>
       <c r="S34" t="n">
-        <v>96.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>56.6</v>
+        <v>16.6</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9805,142 +9809,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>87.71</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>98.9834</t>
+          <t>103.6146</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3965</t>
+          <t>0.412</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1753</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>72.21</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>33.99</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1897</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>88.47</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4085</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1345</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>22.45</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9951,47 +9947,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>682987</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spencer Jones</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20T22:35:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10000,7 +9996,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10014,65 +10010,61 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>65.40000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>32.9</v>
+        <v>41.2</v>
       </c>
       <c r="R35" t="n">
-        <v>32.1</v>
+        <v>36.1</v>
       </c>
       <c r="S35" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>16.6</v>
+        <v>25.5</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10089,12 +10081,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10104,119 +10096,127 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 9/31, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.9% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>45.66</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>91.19</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>103.6146</t>
+          <t>102.0101</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.3287</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>28.15</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>88.47</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1345</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>25.22</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10227,24 +10227,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>SEA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>SEA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>2026-08-20T18:10:00Z</t>
@@ -10257,26 +10257,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Robert Gasser</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>688107</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10290,26 +10290,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>51.5</v>
+        <v>46.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>41.2</v>
+        <v>38.4</v>
       </c>
       <c r="R36" t="n">
         <v>36.1</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U36" t="n">
-        <v>25.5</v>
+        <v>31.4</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10361,27 +10361,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/31, 0 HR</t>
+          <t>Last 7 games: 6/29, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10391,97 +10391,97 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>45.66</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>91.19</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>102.0101</t>
+          <t>102.6335</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.4699</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1971</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3287</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>67.34</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>38.21</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>37.19</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.4023</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.1656</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>27.31</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
@@ -10507,22 +10507,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10542,21 +10542,21 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Robert Gasser</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>688107</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10570,26 +10570,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>46.7</v>
+        <v>36.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>38.4</v>
+        <v>32.7</v>
       </c>
       <c r="R37" t="n">
-        <v>36.1</v>
+        <v>48.2</v>
       </c>
       <c r="S37" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T37" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U37" t="n">
-        <v>31.4</v>
+        <v>83.2</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10641,27 +10641,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10671,112 +10671,112 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>45.17</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>102.6335</t>
+          <t>101.7434</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4699</t>
+          <t>0.3846</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1971</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>73.77</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>67.34</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>38.21</t>
+          <t>34.96</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>22.84</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD37" t="inlineStr">
         <is>
-          <t>0.4023</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>0.1656</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF37" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr"/>
@@ -10787,47 +10787,47 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>642715</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Willy Adames</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -10836,7 +10836,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10850,26 +10850,26 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>36.1</v>
+        <v>36.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>32.7</v>
+        <v>56.1</v>
       </c>
       <c r="R38" t="n">
-        <v>48.2</v>
+        <v>39.6</v>
       </c>
       <c r="S38" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T38" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U38" t="n">
-        <v>83.2</v>
+        <v>39.1</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -10926,22 +10926,22 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10951,112 +10951,112 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>45.17</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.71</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>101.7434</t>
+          <t>98.9834</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.3846</t>
+          <t>0.3965</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1753</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>73.77</t>
+          <t>72.21</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>34.96</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>33.99</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1897</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.4085</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="BG38" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -12317,12 +12317,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -13851,27 +13851,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>543807</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>George Springer</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13881,26 +13881,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13914,26 +13914,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>39.2</v>
+        <v>28.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>41.5</v>
+        <v>55.1</v>
       </c>
       <c r="R49" t="n">
-        <v>41.1</v>
+        <v>70.8</v>
       </c>
       <c r="S49" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T49" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>13.6</v>
+        <v>63.7</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -13985,27 +13985,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -14015,112 +14015,112 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>40.88</t>
+          <t>38.01</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.65</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>100.111</t>
+          <t>99.3262</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.24</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>19.45</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>25.73</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1838</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14131,27 +14131,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>543807</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>George Springer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14161,22 +14161,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -14194,26 +14194,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>28.2</v>
+        <v>39.2</v>
       </c>
       <c r="Q50" t="n">
-        <v>55.1</v>
+        <v>41.5</v>
       </c>
       <c r="R50" t="n">
-        <v>70.8</v>
+        <v>41.1</v>
       </c>
       <c r="S50" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U50" t="n">
-        <v>63.7</v>
+        <v>8.5</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14265,27 +14265,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14295,112 +14295,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>38.01</t>
+          <t>40.88</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>99.3262</t>
+          <t>100.111</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.3769</t>
+          <t>0.431</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.334</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>73.24</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>35.09</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>25.73</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.1838</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.3893</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -15519,24 +15519,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>663662</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Daz Cameron</t>
+          <t>Cedric Mullins</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>2026-08-20T17:10:00Z</t>
@@ -15549,26 +15549,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15582,23 +15582,23 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>31.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>41.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R55" t="n">
         <v>41.1</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U55" t="n">
         <v>24.9</v>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15648,17 +15648,17 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -15668,12 +15668,12 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 3 games: 2/7, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15683,97 +15683,97 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>32.96</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>87.35</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>98.1234</t>
+          <t>97.8501</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3144</t>
+          <t>0.3162</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1035</t>
+          <t>0.1225</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.2665</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>31.59</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.1561</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>26.03</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
@@ -15799,47 +15799,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663662</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Daz Cameron</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15848,7 +15848,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15862,26 +15862,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>45.9</v>
+        <v>31.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="R56" t="n">
-        <v>50.1</v>
+        <v>41.1</v>
       </c>
       <c r="S56" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U56" t="n">
-        <v>22.4</v>
+        <v>24.9</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15916,7 +15916,7 @@
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -15928,19 +15928,19 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="AJ56" t="inlineStr">
         <is>
           <t>0</t>
@@ -15948,12 +15948,12 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 3 games: 2/7, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15963,112 +15963,112 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>16.13</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>87.35</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>103.328</t>
+          <t>98.1234</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.3144</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1035</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1838</t>
+          <t>0.1463</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3893</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16079,22 +16079,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -16109,22 +16109,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -16142,26 +16142,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>37.6</v>
+        <v>45.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>41.2</v>
+        <v>40.5</v>
       </c>
       <c r="R57" t="n">
-        <v>36.1</v>
+        <v>50.1</v>
       </c>
       <c r="S57" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T57" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>14.1</v>
+        <v>22.4</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -16196,7 +16196,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16213,12 +16213,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -16228,12 +16228,12 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -16243,112 +16243,112 @@
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>100.4496</t>
+          <t>103.328</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3406</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>22.21</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1694</t>
+          <t>0.1838</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16359,47 +16359,47 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-21T00:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16422,65 +16422,61 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>41.9</v>
+        <v>37.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>63.7</v>
+        <v>41.2</v>
       </c>
       <c r="R58" t="n">
-        <v>27.6</v>
+        <v>36.1</v>
       </c>
       <c r="S58" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T58" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>18.3</v>
+        <v>14.1</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16497,27 +16493,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16527,104 +16523,112 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>89.78</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>101.4918</t>
+          <t>100.4496</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4007</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.3406</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>12.92</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.2019</t>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="BG58" t="inlineStr"/>
-      <c r="BH58" t="inlineStr"/>
+          <t>25.22</t>
+        </is>
+      </c>
+      <c r="BG58" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH58" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16635,12 +16639,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16665,7 +16669,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -16698,11 +16702,11 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>41.4</v>
+        <v>41.9</v>
       </c>
       <c r="Q59" t="n">
         <v>63.7</v>
@@ -16711,13 +16715,13 @@
         <v>27.6</v>
       </c>
       <c r="S59" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T59" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16731,7 +16735,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16773,27 +16777,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/21, 0 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16803,67 +16807,67 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>89.78</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>100.835</t>
+          <t>101.4918</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4007</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.2927</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>75.72</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>43.11</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.1612</t>
+          <t>0.2019</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
@@ -16911,47 +16915,47 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gary Sánchez</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-21T00:10:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16960,7 +16964,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16974,61 +16978,65 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>42.2</v>
+        <v>41.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>41.2</v>
+        <v>63.7</v>
       </c>
       <c r="R60" t="n">
-        <v>36.1</v>
+        <v>27.6</v>
       </c>
       <c r="S60" t="n">
-        <v>94.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T60" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U60" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -17045,27 +17053,27 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 1 HR</t>
+          <t>Last 7 games: 1/21, 0 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
@@ -17075,112 +17083,104 @@
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>100.835</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.1957</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.3465</t>
+          <t>0.2927</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>75.72</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.2143</t>
+          <t>0.1612</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="BG60" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH60" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -17191,47 +17191,47 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>656775</t>
+          <t>596142</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cedric Mullins</t>
+          <t>Gary Sánchez</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -17240,7 +17240,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17254,26 +17254,26 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>19.3</v>
+        <v>42.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>66.09999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="R61" t="n">
-        <v>41.1</v>
+        <v>36.1</v>
       </c>
       <c r="S61" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T61" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U61" t="n">
-        <v>16.6</v>
+        <v>30.3</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -17325,27 +17325,27 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -17355,112 +17355,112 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>97.8501</t>
+          <t>101.2803</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.3162</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.1225</t>
+          <t>0.1957</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.2665</t>
+          <t>0.3465</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.1561</t>
+          <t>0.2143</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>26.03</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr"/>
@@ -17471,56 +17471,56 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>669394</t>
+          <t>622761</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jake Burger</t>
+          <t>Jorge Mateo</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-21T00:05:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Andrew Alvarez</t>
+          <t>Shane Bieber</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17534,62 +17534,58 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>48.5</v>
+        <v>36.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>22.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="R62" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S62" t="n">
-        <v>92.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T62" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U62" t="n">
-        <v>57.6</v>
+        <v>50.3</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17609,27 +17605,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 2/6 over last 7 games</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 2.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -17639,104 +17635,112 @@
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>102.6757</t>
+          <t>100.3908</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.4227</t>
+          <t>0.3894</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1872</t>
+          <t>0.1566</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3086</t>
+          <t>0.2886</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>75.37</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>58.14</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>41.88</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>31.19</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.1844</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>47.64</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>89.25</t>
+          <t>91.1</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.3542</t>
+          <t>0.5133</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1095</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr"/>
-      <c r="BH62" t="inlineStr"/>
+          <t>26.03</t>
+        </is>
+      </c>
+      <c r="BG62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH62" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17747,32 +17751,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>680869</t>
+          <t>669394</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Jake Burger</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -17782,21 +17786,21 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Andrew Alvarez</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>674841</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17810,58 +17814,62 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>37.5</v>
+        <v>48.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>32.7</v>
+        <v>22.5</v>
       </c>
       <c r="R63" t="n">
-        <v>48.2</v>
+        <v>27.6</v>
       </c>
       <c r="S63" t="n">
-        <v>96.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T63" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U63" t="n">
-        <v>54.7</v>
+        <v>57.6</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC63" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17881,12 +17889,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -17901,7 +17909,7 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 2.4 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -17911,112 +17919,104 @@
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>99.6651</t>
+          <t>102.6757</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.3718</t>
+          <t>0.4227</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1872</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.2785</t>
+          <t>0.3086</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>73.29</t>
+          <t>75.37</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>28.06</t>
+          <t>58.14</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.88</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1799</t>
+          <t>0.1844</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.25</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.3542</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1095</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>21.5</t>
-        </is>
-      </c>
-      <c r="BG63" t="inlineStr">
-        <is>
-          <t>R To L</t>
-        </is>
-      </c>
-      <c r="BH63" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t>18.25</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr"/>
+      <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18027,22 +18027,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>680869</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -18057,17 +18057,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18090,26 +18090,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>46.9</v>
+        <v>37.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>41.2</v>
+        <v>32.7</v>
       </c>
       <c r="R64" t="n">
-        <v>36.1</v>
+        <v>48.2</v>
       </c>
       <c r="S64" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T64" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>21.1</v>
+        <v>54.7</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -18166,137 +18166,137 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>43.14</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>92.08</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>103.555</t>
+          <t>99.6651</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.4061</t>
+          <t>0.3718</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.1596</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.3279</t>
+          <t>0.2785</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>73.29</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>28.06</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>27.17</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1307</t>
+          <t>0.1799</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>7.62</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>89.83</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -18307,47 +18307,47 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>686611</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dylan Crews</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-21T00:05:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -18356,7 +18356,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -18370,62 +18370,58 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>42.6</v>
+        <v>46.9</v>
       </c>
       <c r="Q65" t="n">
-        <v>50.2</v>
+        <v>41.2</v>
       </c>
       <c r="R65" t="n">
-        <v>27.6</v>
+        <v>36.1</v>
       </c>
       <c r="S65" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T65" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U65" t="n">
-        <v>2.5</v>
+        <v>21.1</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18445,12 +18441,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -18460,119 +18456,127 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>90.33</t>
+          <t>92.08</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>101.1127</t>
+          <t>103.555</t>
         </is>
       </c>
       <c r="AR65" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.4061</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>0.1596</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr">
         <is>
-          <t>0.3154</t>
+          <t>0.3279</t>
         </is>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>73.83</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1307</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>90.45</t>
+          <t>89.83</t>
         </is>
       </c>
       <c r="BD65" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BF65" t="inlineStr">
         <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="BG65" t="inlineStr"/>
-      <c r="BH65" t="inlineStr"/>
+          <t>25.22</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI65" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ65" t="inlineStr"/>
@@ -18583,47 +18587,47 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>686611</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Dylan Crews</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Shane Bieber</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>669456</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -18632,7 +18636,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -18646,58 +18650,62 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>36.2</v>
+        <v>42.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>66.09999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="R66" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S66" t="n">
-        <v>52.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T66" t="n">
         <v>50</v>
       </c>
       <c r="U66" t="n">
-        <v>37.8</v>
+        <v>2.5</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC66" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18717,27 +18725,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/8, 1 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.7% barrel, 9.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -18747,112 +18755,104 @@
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>90.33</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>100.3908</t>
+          <t>101.1127</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
         <is>
-          <t>0.3894</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>0.1566</t>
+          <t>0.179</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr">
         <is>
-          <t>0.2886</t>
+          <t>0.3154</t>
         </is>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.83</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>11.74</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>47.64</t>
+          <t>44.49</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>91.1</t>
+          <t>90.45</t>
         </is>
       </c>
       <c r="BD66" t="inlineStr">
         <is>
-          <t>0.5133</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BF66" t="inlineStr">
         <is>
-          <t>26.03</t>
-        </is>
-      </c>
-      <c r="BG66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH66" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="BG66" t="inlineStr"/>
+      <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ66" t="inlineStr"/>
@@ -19975,47 +19975,47 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Jeremy Pena</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20T16:40:00Z</t>
+          <t>2026-08-21T00:10:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -20038,61 +20038,65 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>31.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>55.1</v>
+        <v>63.7</v>
       </c>
       <c r="R71" t="n">
-        <v>70.8</v>
+        <v>27.6</v>
       </c>
       <c r="S71" t="n">
-        <v>44.8</v>
+        <v>88.7</v>
       </c>
       <c r="T71" t="n">
         <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>45.3</v>
+        <v>22.6</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20109,12 +20113,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -20124,12 +20128,12 @@
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/10, 1 HR</t>
+          <t>Last 7 games: 4/27, 1 HR</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20139,112 +20143,104 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>90.07</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>99.7622</t>
+          <t>99.8889</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.3826</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.1397</t>
+          <t>0.1459</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.3326</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>46.41</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>27.08</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.0948</t>
+          <t>0.1821</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>90.15</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4801</t>
+          <t>0.505</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1991</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>26.55</t>
-        </is>
-      </c>
-      <c r="BG71" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH71" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -20255,56 +20251,56 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jeremy Pena</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-21T00:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -20318,62 +20314,58 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>29.7</v>
+        <v>26.5</v>
       </c>
       <c r="Q72" t="n">
-        <v>63.7</v>
+        <v>40.5</v>
       </c>
       <c r="R72" t="n">
-        <v>27.6</v>
+        <v>50.1</v>
       </c>
       <c r="S72" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T72" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U72" t="n">
-        <v>22.6</v>
+        <v>41.2</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -20393,12 +20385,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -20408,12 +20400,12 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 1 HR</t>
+          <t>Last 7 games: 3/11, 1 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20423,104 +20415,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>99.8889</t>
+          <t>99.6064</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3448</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.1459</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.3326</t>
+          <t>0.2948</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>72.56</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.1821</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>39.9</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="BG72" t="inlineStr"/>
-      <c r="BH72" t="inlineStr"/>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="BG72" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20531,32 +20531,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>691781</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Brady House</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-21T00:05:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20566,17 +20566,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -20594,61 +20594,65 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>26.5</v>
+        <v>40.1</v>
       </c>
       <c r="Q73" t="n">
-        <v>40.5</v>
+        <v>50.2</v>
       </c>
       <c r="R73" t="n">
-        <v>50.1</v>
+        <v>27.6</v>
       </c>
       <c r="S73" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T73" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U73" t="n">
-        <v>41.2</v>
+        <v>32.9</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20665,12 +20669,12 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -20680,12 +20684,12 @@
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/11, 1 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20695,112 +20699,104 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>9.27</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>89.45</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>99.6064</t>
+          <t>101.7139</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.3448</t>
+          <t>0.4225</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.2948</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>72.56</t>
+          <t>73.31</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>31.16</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1391</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>44.49</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.45</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="BG73" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH73" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20811,47 +20807,47 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>691781</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brady House</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-21T00:05:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -20860,7 +20856,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -20874,65 +20870,61 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>40.1</v>
+        <v>35.6</v>
       </c>
       <c r="Q74" t="n">
-        <v>50.2</v>
+        <v>32.7</v>
       </c>
       <c r="R74" t="n">
-        <v>27.6</v>
+        <v>48.2</v>
       </c>
       <c r="S74" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T74" t="n">
         <v>50</v>
       </c>
       <c r="U74" t="n">
-        <v>32.9</v>
+        <v>52.1</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -20949,12 +20941,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -20964,12 +20956,12 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -20979,104 +20971,112 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>9.27</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>89.45</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>101.7139</t>
+          <t>104.3344</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.4225</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>73.31</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>31.16</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1391</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>90.45</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="BG74" t="inlineStr"/>
-      <c r="BH74" t="inlineStr"/>
+          <t>21.5</t>
+        </is>
+      </c>
+      <c r="BG74" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH74" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -21087,32 +21087,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>687551</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Drew Gilbert</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T17:10:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -21136,7 +21136,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21150,26 +21150,26 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>35.6</v>
+        <v>16.4</v>
       </c>
       <c r="Q75" t="n">
-        <v>32.7</v>
+        <v>56.1</v>
       </c>
       <c r="R75" t="n">
-        <v>48.2</v>
+        <v>39.6</v>
       </c>
       <c r="S75" t="n">
         <v>93.2</v>
       </c>
       <c r="T75" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U75" t="n">
-        <v>52.1</v>
+        <v>37.8</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -21221,12 +21221,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.5% barrel, 1.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21251,112 +21251,112 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>34.61</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.32</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>104.3344</t>
+          <t>97.7642</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3633</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1181</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.3057</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>40.42</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>20.04</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.1376</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>46.61</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.19</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.4085</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21367,47 +21367,47 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>687551</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Drew Gilbert</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20T17:10:00Z</t>
+          <t>2026-08-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Grant Holmes</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21416,7 +21416,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -21430,26 +21430,26 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>16.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q76" t="n">
-        <v>56.1</v>
+        <v>50</v>
       </c>
       <c r="R76" t="n">
-        <v>39.6</v>
+        <v>50.1</v>
       </c>
       <c r="S76" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T76" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U76" t="n">
-        <v>37.8</v>
+        <v>26.4</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -21484,7 +21484,7 @@
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr"/>
@@ -21501,27 +21501,27 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.9% barrel, 23.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 18.1 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21531,112 +21531,112 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>34.61</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>86.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>97.7642</t>
+          <t>100.1171</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.3633</t>
+          <t>0.361</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1181</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.3057</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1376</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>90.19</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.4085</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.1768</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21647,47 +21647,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20T18:10:00Z</t>
+          <t>2026-08-20T16:40:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Grant Holmes</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>656550</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21696,7 +21696,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21710,26 +21710,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>21.6</v>
+        <v>31.6</v>
       </c>
       <c r="Q77" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="R77" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="S77" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="T77" t="n">
         <v>50</v>
       </c>
-      <c r="R77" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="S77" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="T77" t="n">
-        <v>75</v>
-      </c>
       <c r="U77" t="n">
-        <v>26.4</v>
+        <v>33.7</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21764,7 +21764,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21781,27 +21781,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 2/9, 1 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 18.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.8% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21811,112 +21811,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.07</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.1171</t>
+          <t>99.7622</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>0.3826</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1397</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.0948</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.15</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4801</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1768</t>
+          <t>0.1991</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>26.55</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -21927,22 +21927,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>807727</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Charles McAdoo</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -21957,22 +21957,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Landen Roupp</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>694738</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -21994,22 +21994,22 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>38.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>23.2</v>
+        <v>41.5</v>
       </c>
       <c r="R78" t="n">
-        <v>39.6</v>
+        <v>41.1</v>
       </c>
       <c r="S78" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T78" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U78" t="n">
-        <v>37.8</v>
+        <v>45</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22044,7 +22044,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -22061,27 +22061,27 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22091,112 +22091,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>101.2217</t>
+          <t>97.1341</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.396</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1716</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1978</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>86.93</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.3893</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22207,22 +22207,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>807727</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charles McAdoo</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -22237,26 +22237,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Landen Roupp</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>694738</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22274,22 +22274,22 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>25.1</v>
+        <v>38.8</v>
       </c>
       <c r="Q79" t="n">
-        <v>41.5</v>
+        <v>23.2</v>
       </c>
       <c r="R79" t="n">
-        <v>41.1</v>
+        <v>39.6</v>
       </c>
       <c r="S79" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22324,7 +22324,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22341,27 +22341,27 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22371,112 +22371,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>97.1341</t>
+          <t>101.2217</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1716</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>25.85</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.1978</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>86.93</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.3893</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -47366,7 +47366,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>66.40000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -47399,7 +47399,7 @@
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>71.59999999999999</v>
+        <v>51.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -47451,22 +47451,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -49322,7 +49322,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>28.1</v>
+        <v>30.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -49422,7 +49422,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -49967,12 +49967,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -49982,7 +49982,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/32, 0 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
